--- a/AAII_Financials/Quarterly/ABNB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ABNB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>ABNB</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3608000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2678000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2778000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4095000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3096000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2272000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2480000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3732000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2748000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2142000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2218000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3397000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2484000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1818000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1901500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2884400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2104100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1508900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1532200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2237400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1335200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>886900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>859300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1342300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>334800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>841800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1106800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1645800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1213700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>839000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E9" s="3">
         <v>581000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>487000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>549000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>544000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>506000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>427000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>465000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>506000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>480000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>384000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>459000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>432000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>428000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>604900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>691100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>648400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>595600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>520500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>539900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>502600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>440000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>539300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>393400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>321700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>499600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>507900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>532100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>524000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>447300</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2097000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2291000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3546000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2552000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1766000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2053000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3267000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2242000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1662000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1834000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2938000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2052000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1390000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1296600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2193300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1455700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>913300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1011700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1697500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>832600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>446900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>320000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>948900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>13100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>342200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>598900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1113700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>689700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>391700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E12" s="3">
         <v>638000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>589000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>587000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>610000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>568000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>538000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>524000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>519000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>475000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>432000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>419000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>451000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>420000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>397800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>366200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>375100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>362900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>367800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>344400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>349700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>363100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>2062200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>213900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>217900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>258800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>282900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>276400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>232300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>185100</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,38 +1299,41 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3">
         <v>-38000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-7000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="3">
         <v>45000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>17</v>
       </c>
@@ -1326,101 +1346,104 @@
       <c r="P14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>88700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>489200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>18300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>114200</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>13700</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E15" s="3">
         <v>22000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>21000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>14000</v>
       </c>
       <c r="L15" s="3">
         <v>14000</v>
       </c>
       <c r="M15" s="3">
+        <v>14000</v>
+      </c>
+      <c r="N15" s="3">
         <v>3000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2850000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2592000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2509000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2470000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2484000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2234000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2050000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2207000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2251000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2041000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2714000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1901000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1961000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1823000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1666700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1680900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1735300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1514100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1456600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1385500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1386500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1711100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3959400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>923600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>918000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1167300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1444500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1413200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1313800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1145000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>758000</v>
+      </c>
+      <c r="E18" s="3">
         <v>86000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>269000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1625000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>612000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>430000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1525000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>497000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>101000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-496000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1496000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>523000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>234800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1203500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>368800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>75600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>851900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-51300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-824200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3100100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>418700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-583200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-325500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-337700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>232600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-100100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-306000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,197 +1748,204 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>45000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13000</v>
       </c>
-      <c r="G20" s="3">
-        <v>23000</v>
-      </c>
       <c r="H20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I20" s="3">
         <v>38000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-3000</v>
       </c>
       <c r="K20" s="3">
         <v>-3000</v>
       </c>
       <c r="L20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M20" s="3">
         <v>10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>79000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>38000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>114400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>72100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-297000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-828200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-31600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>51300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>30600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>768000</v>
+      </c>
+      <c r="E21" s="3">
         <v>110000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>231500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1634000</v>
       </c>
-      <c r="G21" s="3">
-        <v>610000</v>
-      </c>
       <c r="H21" s="3">
+        <v>616000</v>
+      </c>
+      <c r="I21" s="3">
         <v>25000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>446800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1543000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>514000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>105000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-572000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1495000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>494000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>362100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1288400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>416600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>105600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>890800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-14900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1082900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3895900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>430400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-594200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-323200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-301100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>336100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-66400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-256100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>17</v>
+      <c r="D22" s="3">
+        <v>37000</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>17</v>
@@ -1916,8 +1956,8 @@
       <c r="G22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
+      <c r="H22" s="3">
+        <v>6000</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>17</v>
@@ -1943,240 +1983,249 @@
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3">
         <v>5100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>44700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>64100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3200</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>2500</v>
       </c>
       <c r="AE22" s="3">
         <v>2500</v>
       </c>
       <c r="AF22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AG22" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>897000</v>
+      </c>
+      <c r="E23" s="3">
         <v>281000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>393000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1792000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>779000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>173000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>622000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1735000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>681000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>293000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-383000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1679000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>676000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>130000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>344100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1269900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>383100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>72200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>850500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-57000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1165900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3992500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>307100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-639400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-357100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-342100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>281300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-72000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-279000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E24" s="3">
         <v>121000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>52000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>418000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>137000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>161000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>367000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>126000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-34000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2695000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>25400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-104700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>87700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-63800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>225500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E26" s="3">
         <v>160000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>341000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1374000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>642000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>154000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>461000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1368000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>555000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>264000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-349000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4374000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>650000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>117000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>318700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1214300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>378800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>54500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>833900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-68200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1172200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3887900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>219300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-575600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-340600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-351500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>266700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-297400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-292000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E27" s="3">
         <v>160000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>341000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1374000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>642000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>154000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>461000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1368000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>555000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>264000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-349000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4374000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>650000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>117000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>318700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1214300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>378800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>54500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>833900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-68200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1172200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3887900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>219300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-575600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-340600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-351500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>266700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-297400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-292000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-45000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-23000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-38000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3000</v>
       </c>
       <c r="K32" s="3">
         <v>3000</v>
       </c>
       <c r="L32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-79000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-38000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-114400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-72100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>297000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>828200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>51800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>31600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-51300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-30600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-28800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E33" s="3">
         <v>160000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>341000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1374000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>642000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>154000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>461000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1368000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>555000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>264000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-349000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4374000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>650000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>318700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1214300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>378800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>54500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>833900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-68200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1172200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3887900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>219300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-575600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-340600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-351500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>266700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-297400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-292000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E35" s="3">
         <v>160000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>341000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1374000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>642000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>154000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>461000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1368000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>555000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>264000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-349000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4374000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>650000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>318700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1214300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>378800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>54500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>833900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-68200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1172200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3887900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>219300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-575600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-340600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-351500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>266700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-297400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-292000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,83 +3438,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6821000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7037000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6560000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7528000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7402000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7600000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6864000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7670000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7882000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7829000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6874000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8175000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7905000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8166000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7378000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7523700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7838000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6886600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6067400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5994700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5672700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4482600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5480600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2664400</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>17</v>
       </c>
@@ -3444,83 +3531,86 @@
       <c r="AF41" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5248000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4968000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4454000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4156000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3954000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3892000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3747000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3583000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3369000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3264000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3197000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2787000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2435000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2428000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2244000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2103900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2057500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2435700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2255000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1926000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1755300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2086700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>910700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1830800</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>17</v>
       </c>
@@ -3536,31 +3626,34 @@
       <c r="AF42" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E43" s="3">
         <v>191000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>186000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>180000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>186000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>174000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>147000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>175000</v>
       </c>
       <c r="K43" s="3">
         <v>175000</v>
@@ -3569,50 +3662,50 @@
         <v>175000</v>
       </c>
       <c r="M43" s="3">
+        <v>175000</v>
+      </c>
+      <c r="N43" s="3">
         <v>205000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>206000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>218000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>185000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4983000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4983500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7670100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6260600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3858000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4089200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6456800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4177600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2371100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2539300</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>17</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3672,8 +3768,8 @@
       <c r="P44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3720,83 +3816,86 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12308000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10647000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7597000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7674000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11638000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9629000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6422000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6585000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10405000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8772000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6233000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6083000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9167000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7777000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>256000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>255400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>260100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>178600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>205900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>211000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>211200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>179800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>154000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>177700</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>17</v>
       </c>
@@ -3812,83 +3911,86 @@
       <c r="AF45" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25479000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23601000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18797000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19538000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23180000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21295000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17180000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18319000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22252000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20393000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16509000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17523000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20052000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18869000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14861000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14866500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17825600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15761400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12386400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12220900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14096000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10926600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8916400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7212200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>17</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3942,14 +4047,14 @@
       <c r="N47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O47" s="3">
-        <v>79000</v>
+      <c r="O47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P47" s="3">
         <v>79000</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3972,15 +4077,15 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA47" s="3">
         <v>13000</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>17</v>
       </c>
@@ -3996,83 +4101,86 @@
       <c r="AF47" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="3">
         <v>224000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>272000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>276000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>277000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>222000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>262000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>273000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>282000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>252000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>270000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>263000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>260000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>259000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>272700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>282700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>405800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>428600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>453900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>482300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>512000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>654300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>615700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>17</v>
       </c>
@@ -4088,83 +4196,86 @@
       <c r="AF48" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E49" s="3">
         <v>767000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>803000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>773000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>776000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>775000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>846000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>783000</v>
       </c>
       <c r="K49" s="3">
         <v>783000</v>
       </c>
       <c r="L49" s="3">
+        <v>783000</v>
+      </c>
+      <c r="M49" s="3">
         <v>786000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>819000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>676000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>679000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>682000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>684000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>684700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>691800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>698500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>704900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>711600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>718200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>723300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>731700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>728300</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>17</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,83 +4481,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600000</v>
+      </c>
+      <c r="E52" s="3">
         <v>519000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>282000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>335000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>332000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>250000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>272000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>207000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>187000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>190000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>184000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>195000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>115000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>128000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>234000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>252700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>258900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>202600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>188600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>195500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>188300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>177100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>189200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>159200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>17</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,83 +4671,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28754000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26828000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22208000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23064000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26992000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25056000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20959000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22172000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26320000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24537000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20645000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21439000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21188000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20018000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16038000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16076600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19059100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17068400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13708500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13582000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15484800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12339100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10491500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8728500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>17</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,83 +4838,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E57" s="3">
         <v>180000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>232000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>181000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>221000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>186000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>142000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>181000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>163000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>184000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>141000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>163000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>161000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4920000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4958000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7604800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6232800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3833800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4037600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6399400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4131600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2261200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2400400</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>17</v>
       </c>
@@ -4800,53 +4931,56 @@
       <c r="AF57" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E58" s="3">
         <v>59000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2067000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2065000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2064000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2057000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>63000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>54000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>59000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>61000</v>
       </c>
       <c r="M58" s="3">
         <v>61000</v>
       </c>
       <c r="N58" s="3">
+        <v>61000</v>
+      </c>
+      <c r="O58" s="3">
         <v>54000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>50000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4869,14 +5003,14 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>26800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>27900</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>17</v>
       </c>
@@ -4892,83 +5026,86 @@
       <c r="AF58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16076000</v>
+      </c>
+      <c r="E59" s="3">
         <v>14178000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9625000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10037000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14927000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12789000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8403000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9085000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13853000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12093000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8193000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7608000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11669000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10112000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3058000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3057300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3682400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3540900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2525500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2521700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3097000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2441600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2851800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1955800</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>17</v>
       </c>
@@ -4984,83 +5121,86 @@
       <c r="AF59" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18092000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16364000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13649000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14039000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18816000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16730000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10161000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11336000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15828000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14139000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9950000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9821000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13624000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12212000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7978000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8015300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11287200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9773800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6359300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6559300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9496400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6573200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5139800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4384100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>17</v>
       </c>
@@ -5076,83 +5216,86 @@
       <c r="AF60" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2476000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2475000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>204000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>213000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>218000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>223000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2231000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2205000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2215000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2229000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2243000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2255000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2274000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2288000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1987000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1985700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1984600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1983600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1982500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1981500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1980500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1979400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1815600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1811300</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5168,83 +5311,86 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E62" s="3">
         <v>353000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>156000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>202000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>176000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>166000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>155000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>143000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>275000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>273000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>287000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>240000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>231000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>227000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>513000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>535500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>542300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>573700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>590900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>592300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>614800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>627100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>634400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>677900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>17</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,83 +5691,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20955000</v>
+      </c>
+      <c r="E66" s="3">
         <v>19192000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14009000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14454000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19210000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17119000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12547000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13684000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18318000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16641000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12480000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12316000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16129000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14727000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10478000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10536500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13814100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12331000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8932800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9133100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12091600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9179700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7589700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6873300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>17</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,11 +6086,11 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>3231500</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,83 +6201,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6653000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6403000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5502000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4748000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5258000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4883000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4225000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3843000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4109000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3914000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3425000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2324000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6198000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6341000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5965000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5783400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5997700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6376500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6357700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6412200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7246100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7177900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-6005700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2117900</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>17</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,83 +6581,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7799000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7636000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8199000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8610000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7782000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7937000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8412000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8488000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8002000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7896000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8165000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9123000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5059000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5291000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5560000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5540100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5245000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4737400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4775700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4448900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3393200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3159400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2901800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1376300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>17</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E81" s="3">
         <v>160000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>341000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1374000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>642000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>154000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>461000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1368000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>555000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>264000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-349000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4374000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>650000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>318700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1214300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>378800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>54500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>833900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-68200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1172200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3887900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>219300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-575600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-340600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-351500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>266700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-297400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-292000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-12000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>14000</v>
       </c>
       <c r="H83" s="3">
         <v>14000</v>
       </c>
       <c r="I83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-15000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>26000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>33700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>35500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>38300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32400</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD83" s="3">
         <v>37800</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1270000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1708000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>526000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1356000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>975000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1789000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>466000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1078000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1051000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1923000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>63000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1325000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>909000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1587000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>462700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>965600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>799700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1202000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>258900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>534700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>789700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>606400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-139100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>335700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-256500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-569800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-196400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-46600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>151600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7527,8 +7748,8 @@
       <c r="P91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q91" s="3">
-        <v>-6000</v>
+      <c r="Q91" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R91" s="3">
         <v>-6000</v>
@@ -7540,43 +7761,46 @@
         <v>-6000</v>
       </c>
       <c r="U91" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-4500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5500</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-7700</v>
       </c>
       <c r="X91" s="3">
         <v>-7700</v>
       </c>
       <c r="Y91" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-26200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-349000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-461000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-206000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-91000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-151000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-220000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-202000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-110000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-84000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-475000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-364000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-183000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-143300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-55800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>368000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-197000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-329400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-175700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>325500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1172300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>895700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-237300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-581100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>2300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-297100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>17900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-109700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7929,8 +8163,8 @@
       <c r="P96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2970000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1450000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4850000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>328000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2145000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1330000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5187000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>811000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2134000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1171000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3712000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>167000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2286000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-764400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3574100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1446000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2203500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-146500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2323400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2333500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1567500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1766600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1030000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2543400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-339200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>170400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1420500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>624900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1479800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E101" s="3">
         <v>207000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-354000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>319000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-91000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-111000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>162000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-142000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>53000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>79000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>288000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-317000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-311000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>288900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-318000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-311300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-50900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-103300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>16500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-72300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>98900</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD101" s="3">
         <v>51700</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AF101" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1464000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4099000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1227000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3731000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1694000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3990000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1438000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3992000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1661000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3862000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1421000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2893000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1109000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3769000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-156100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2982300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2302400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3211900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-145900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2079200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3466900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>817300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2622100</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-271300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>17</v>
       </c>
     </row>
